--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487166_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487166_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>E. GUTIERREZ O´CALLAGHAN</t>
+          <t>A. DEL VAL IBAÑEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9004</v>
+        <v>-0.5251</v>
       </c>
       <c r="E2" t="n">
-        <v>1.9709</v>
+        <v>0.7955</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.0705</v>
+        <v>-1.3206</v>
       </c>
       <c r="G2" t="n">
-        <v>-3.7021</v>
+        <v>-0.7697000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.62</v>
+        <v>0.0507</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.0821</v>
+        <v>-0.8204</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6694</v>
+        <v>0.9522</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5637</v>
+        <v>0.9522</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1057</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-4.3714</v>
+        <v>-1.7219</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.1837</v>
+        <v>-0.9014</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.1878</v>
+        <v>-0.8204</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.772</v>
+        <v>0.579</v>
       </c>
       <c r="Q2" t="n">
-        <v>-4.0532</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>3.2811</v>
+        <v>0.579</v>
       </c>
       <c r="S2" t="n">
-        <v>2.0187</v>
+        <v>-0.3345</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9989</v>
+        <v>-0.1566</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0198</v>
+        <v>-0.1778</v>
       </c>
       <c r="V2" t="n">
-        <v>3.3558</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>3.3558</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. DEL VAL IBAÑEZ</t>
+          <t>E. GUTIERREZ O´CALLAGHAN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.7789</v>
+        <v>-0.7901</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5952</v>
+        <v>0.3874</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.3742</v>
+        <v>-1.1776</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.7697000000000001</v>
+        <v>-3.7021</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0507</v>
+        <v>-1.62</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.8204</v>
+        <v>-2.0821</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9522</v>
+        <v>0.6694</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9522</v>
+        <v>0.5637</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.1057</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.7219</v>
+        <v>-4.3714</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9014</v>
+        <v>-2.1837</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8204</v>
+        <v>-2.1878</v>
       </c>
       <c r="P3" t="n">
-        <v>0.579</v>
+        <v>-0.772</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-4.0532</v>
       </c>
       <c r="R3" t="n">
-        <v>0.579</v>
+        <v>3.2811</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5883</v>
+        <v>0.3282</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3569</v>
+        <v>0.4155</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2313</v>
+        <v>-0.0873</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>3.3558</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>3.3558</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.4447</v>
+        <v>-1.518</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0136</v>
+        <v>-0.1137</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.4311</v>
+        <v>-1.4043</v>
       </c>
       <c r="G4" t="n">
         <v>-1.6106</v>
@@ -766,13 +766,13 @@
         <v>0.193</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0271</v>
+        <v>-0.1005</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4891</v>
+        <v>0.389</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5162</v>
+        <v>-0.4895</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.7718</v>
+        <v>-1.7192</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.2175</v>
+        <v>-1.0579</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5543</v>
+        <v>-0.6613</v>
       </c>
       <c r="G5" t="n">
         <v>-1.3551</v>
@@ -844,13 +844,13 @@
         <v>0.193</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1309</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3569</v>
+        <v>-0.1973</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2261</v>
+        <v>0.119</v>
       </c>
       <c r="V5" t="n">
         <v>-0.2859</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. HERNANDEZ BLANCO</t>
+          <t>R. POPA ANDREI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.0708</v>
+        <v>-1.8849</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2444</v>
+        <v>0.9421</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.8265</v>
+        <v>-2.827</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.188</v>
+        <v>-4.1841</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8746</v>
+        <v>-2.367</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.3134</v>
+        <v>-1.8172</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.4784</v>
+        <v>0.3074</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7347</v>
+        <v>-0.1968</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.2131</v>
+        <v>0.5041</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.7096</v>
+        <v>-4.4915</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.6093</v>
+        <v>-2.1702</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.1003</v>
+        <v>-2.3213</v>
       </c>
       <c r="P6" t="n">
-        <v>0.772</v>
+        <v>2.8951</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.965</v>
+        <v>-0.386</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7371</v>
+        <v>3.2811</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9591</v>
+        <v>-0.5959</v>
       </c>
       <c r="T6" t="n">
-        <v>1.1991</v>
+        <v>-0.4931</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2399</v>
+        <v>-0.1028</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.5138</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.614</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. POPA ANDREI</t>
+          <t>P. HERNANDEZ BLANCO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.1437</v>
+        <v>-2.5716</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7637</v>
+        <v>-0.986</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.9073</v>
+        <v>-1.5856</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.1841</v>
+        <v>-3.188</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.367</v>
+        <v>-0.8746</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.8172</v>
+        <v>-2.3134</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3074</v>
+        <v>-0.4784</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1968</v>
+        <v>0.7347</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5041</v>
+        <v>-1.2131</v>
       </c>
       <c r="M7" t="n">
-        <v>-4.4915</v>
+        <v>-2.7096</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.1702</v>
+        <v>-1.6093</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.3213</v>
+        <v>-1.1003</v>
       </c>
       <c r="P7" t="n">
-        <v>2.8951</v>
+        <v>0.772</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.386</v>
+        <v>-0.965</v>
       </c>
       <c r="R7" t="n">
-        <v>3.2811</v>
+        <v>1.7371</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8546</v>
+        <v>0.4584</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6715</v>
+        <v>0.4574</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1831</v>
+        <v>0.001</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.614</v>
       </c>
       <c r="W7" t="n">
-        <v>1.5138</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.5138</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.4048</v>
+        <v>-3.6854</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.5549</v>
+        <v>-2.7552</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8499</v>
+        <v>-0.9302</v>
       </c>
       <c r="G8" t="n">
         <v>-0.7127</v>
@@ -1078,13 +1078,13 @@
         <v>1.9301</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.499</v>
+        <v>-0.7796</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1917</v>
+        <v>-0.0086</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6907</v>
+        <v>-0.7711</v>
       </c>
       <c r="V8" t="n">
         <v>-1.228</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.6988</v>
+        <v>-4.1445</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.9882</v>
+        <v>-2.4875</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.7106</v>
+        <v>-1.657</v>
       </c>
       <c r="G9" t="n">
         <v>-3.2195</v>
@@ -1156,13 +1156,13 @@
         <v>1.3511</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9003</v>
+        <v>-0.346</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5354</v>
+        <v>-0.0347</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3649</v>
+        <v>-0.3113</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.6381</v>
+        <v>-4.8449</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.394</v>
+        <v>-2.815</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.244</v>
+        <v>-2.0299</v>
       </c>
       <c r="G10" t="n">
         <v>-4.4399</v>
@@ -1234,13 +1234,13 @@
         <v>2.5091</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.5216</v>
+        <v>-0.7284</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8632</v>
+        <v>-0.2842</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6584</v>
+        <v>-0.4442</v>
       </c>
       <c r="V10" t="n">
         <v>-1.7997</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.8186</v>
+        <v>-5.2336</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.2462</v>
+        <v>-3.3668</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5724</v>
+        <v>-1.8668</v>
       </c>
       <c r="G11" t="n">
         <v>-5.5864</v>
@@ -1312,13 +1312,13 @@
         <v>1.9301</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1164</v>
+        <v>-0.5314</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0417</v>
+        <v>-0.1622</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0747</v>
+        <v>-0.3692</v>
       </c>
       <c r="V11" t="n">
         <v>1.2702</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.7009</v>
+        <v>-6.761</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.3379</v>
+        <v>-2.3177</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.363</v>
+        <v>-4.4433</v>
       </c>
       <c r="G12" t="n">
         <v>-4.604</v>
@@ -1390,13 +1390,13 @@
         <v>2.3161</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.5831</v>
+        <v>-0.6431</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1898</v>
+        <v>-0.1695</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3933</v>
+        <v>-0.4736</v>
       </c>
       <c r="V12" t="n">
         <v>-1.5138</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-34.5707</v>
+        <v>-33.6783</v>
       </c>
       <c r="E13" t="n">
-        <v>-14.6669</v>
+        <v>-13.7748</v>
       </c>
       <c r="F13" t="n">
-        <v>-19.9038</v>
+        <v>-19.9036</v>
       </c>
       <c r="G13" t="n">
         <v>-33.3721</v>
@@ -1468,13 +1468,13 @@
         <v>19.3008</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.2435</v>
+        <v>-3.3511</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1366</v>
+        <v>-0.2443</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.1066</v>
+        <v>-3.106800000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-0.8154000000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>12.047</v>
+        <v>12.0943</v>
       </c>
       <c r="E14" t="n">
-        <v>9.1928</v>
+        <v>8.8924</v>
       </c>
       <c r="F14" t="n">
-        <v>2.8542</v>
+        <v>3.2019</v>
       </c>
       <c r="G14" t="n">
         <v>8.345599999999999</v>
@@ -1546,13 +1546,13 @@
         <v>2.5091</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9293</v>
+        <v>0.9766</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9782999999999999</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0489</v>
+        <v>0.2987</v>
       </c>
       <c r="V14" t="n">
         <v>1.228</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.9826</v>
+        <v>7.6304</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7132</v>
+        <v>3.0136</v>
       </c>
       <c r="F15" t="n">
-        <v>4.2694</v>
+        <v>4.6168</v>
       </c>
       <c r="G15" t="n">
         <v>6.8828</v>
@@ -1624,13 +1624,13 @@
         <v>2.3161</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2862</v>
+        <v>0.3615</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4164</v>
+        <v>-0.116</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1302</v>
+        <v>0.4775</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.1555</v>
+        <v>5.4827</v>
       </c>
       <c r="E16" t="n">
-        <v>5.1983</v>
+        <v>5.4988</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0428</v>
+        <v>-0.016</v>
       </c>
       <c r="G16" t="n">
         <v>3.0258</v>
@@ -1702,13 +1702,13 @@
         <v>0.579</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2333</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.238</v>
+        <v>0.0625</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0046</v>
+        <v>0.0314</v>
       </c>
       <c r="V16" t="n">
         <v>2.1701</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. SALAZAR ORTEGA</t>
+          <t>B. MENDIA SANGRONIZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.9022</v>
+        <v>4.5737</v>
       </c>
       <c r="E17" t="n">
-        <v>2.805</v>
+        <v>0.6677</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0971</v>
+        <v>3.906</v>
       </c>
       <c r="G17" t="n">
-        <v>5.4046</v>
+        <v>3.6963</v>
       </c>
       <c r="H17" t="n">
-        <v>2.9477</v>
+        <v>1.7606</v>
       </c>
       <c r="I17" t="n">
-        <v>2.4569</v>
+        <v>1.9357</v>
       </c>
       <c r="J17" t="n">
-        <v>5.4444</v>
+        <v>2.4947</v>
       </c>
       <c r="K17" t="n">
-        <v>3.3687</v>
+        <v>1.7542</v>
       </c>
       <c r="L17" t="n">
-        <v>2.0757</v>
+        <v>0.7405</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0398</v>
+        <v>1.2016</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.421</v>
+        <v>0.0064</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3813</v>
+        <v>1.1953</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.7021</v>
+        <v>-0.772</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.0532</v>
+        <v>-3.0881</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3511</v>
+        <v>2.3161</v>
       </c>
       <c r="S17" t="n">
-        <v>1.5857</v>
+        <v>0.7917999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7998</v>
+        <v>0.4035</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7859</v>
+        <v>0.3883</v>
       </c>
       <c r="V17" t="n">
-        <v>0.614</v>
+        <v>0.8576</v>
       </c>
       <c r="W17" t="n">
-        <v>0.614</v>
+        <v>0.8576</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B. MENDIA SANGRONIZ</t>
+          <t>I. SALAZAR ORTEGA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.7124</v>
+        <v>4.0459</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0333</v>
+        <v>2.4045</v>
       </c>
       <c r="F18" t="n">
-        <v>3.7457</v>
+        <v>1.6414</v>
       </c>
       <c r="G18" t="n">
-        <v>3.6963</v>
+        <v>5.4046</v>
       </c>
       <c r="H18" t="n">
-        <v>1.7606</v>
+        <v>2.9477</v>
       </c>
       <c r="I18" t="n">
-        <v>1.9357</v>
+        <v>2.4569</v>
       </c>
       <c r="J18" t="n">
-        <v>2.4947</v>
+        <v>5.4444</v>
       </c>
       <c r="K18" t="n">
-        <v>1.7542</v>
+        <v>3.3687</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7405</v>
+        <v>2.0757</v>
       </c>
       <c r="M18" t="n">
-        <v>1.2016</v>
+        <v>-0.0398</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0064</v>
+        <v>-0.421</v>
       </c>
       <c r="O18" t="n">
-        <v>1.1953</v>
+        <v>0.3813</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.772</v>
+        <v>-2.7021</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.0881</v>
+        <v>-4.0532</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3161</v>
+        <v>1.3511</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0694</v>
+        <v>0.7294</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2974</v>
+        <v>0.3993</v>
       </c>
       <c r="U18" t="n">
-        <v>0.228</v>
+        <v>0.3301</v>
       </c>
       <c r="V18" t="n">
-        <v>0.8576</v>
+        <v>0.614</v>
       </c>
       <c r="W18" t="n">
-        <v>0.8576</v>
+        <v>0.614</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. NDIAYE SOW</t>
+          <t>I. PEDROSA BELLES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.4439</v>
+        <v>1.2282</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5977</v>
+        <v>1.1187</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8462</v>
+        <v>0.1095</v>
       </c>
       <c r="G19" t="n">
-        <v>1.7697</v>
+        <v>1.8818</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.1935</v>
+        <v>0.8023</v>
       </c>
       <c r="I19" t="n">
-        <v>2.9632</v>
+        <v>1.0796</v>
       </c>
       <c r="J19" t="n">
-        <v>1.0153</v>
+        <v>1.5613</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.0197</v>
+        <v>0.8694</v>
       </c>
       <c r="L19" t="n">
-        <v>2.035</v>
+        <v>0.6919</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7544</v>
+        <v>0.3206</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1738</v>
+        <v>-0.06710000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>0.9282</v>
+        <v>0.3877</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.3511</v>
+        <v>0.193</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.0881</v>
+        <v>-0.386</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7371</v>
+        <v>0.579</v>
       </c>
       <c r="S19" t="n">
-        <v>1.6392</v>
+        <v>-0.2327</v>
       </c>
       <c r="T19" t="n">
-        <v>1.1567</v>
+        <v>-0.0565</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4825</v>
+        <v>-0.1762</v>
       </c>
       <c r="V19" t="n">
         <v>-0.614</v>
       </c>
       <c r="W19" t="n">
-        <v>1.5138</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.1278</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.2192</v>
+        <v>1.1987</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5611</v>
+        <v>-0.6612</v>
       </c>
       <c r="F20" t="n">
-        <v>1.7803</v>
+        <v>1.86</v>
       </c>
       <c r="G20" t="n">
         <v>1.636</v>
@@ -2014,13 +2014,13 @@
         <v>1.5441</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8414</v>
+        <v>0.8209</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1917</v>
+        <v>0.0916</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6497000000000001</v>
+        <v>0.7294</v>
       </c>
       <c r="V20" t="n">
         <v>0.2859</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. ERRASTI UGARTE</t>
+          <t>M. NDIAYE SOW</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6811</v>
+        <v>0.8966</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6086</v>
+        <v>-0.0031</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2897</v>
+        <v>0.8997000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2415</v>
+        <v>1.7697</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3344</v>
+        <v>-1.1935</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.09279999999999999</v>
+        <v>2.9632</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1922</v>
+        <v>1.0153</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4347</v>
+        <v>-1.0197</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6269</v>
+        <v>2.035</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4338</v>
+        <v>0.7544</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1003</v>
+        <v>-0.1738</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5341</v>
+        <v>0.9282</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.193</v>
+        <v>-1.3511</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.965</v>
+        <v>-3.0881</v>
       </c>
       <c r="R21" t="n">
-        <v>0.772</v>
+        <v>1.7371</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6326000000000001</v>
+        <v>1.0919</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5486</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0839</v>
+        <v>0.536</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.614</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.5138</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-2.1278</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. PEDROSA BELLES</t>
+          <t>M. ERRASTI UGARTE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3392</v>
+        <v>0.7614</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8183</v>
+        <v>-0.6086</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4791</v>
+        <v>1.37</v>
       </c>
       <c r="G22" t="n">
-        <v>1.8818</v>
+        <v>0.2415</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8023</v>
+        <v>0.3344</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0796</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>1.5613</v>
+        <v>-0.1922</v>
       </c>
       <c r="K22" t="n">
-        <v>0.8694</v>
+        <v>0.4347</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6919</v>
+        <v>-0.6269</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3206</v>
+        <v>0.4338</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.06710000000000001</v>
+        <v>-0.1003</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3877</v>
+        <v>0.5341</v>
       </c>
       <c r="P22" t="n">
-        <v>0.193</v>
+        <v>-0.193</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.386</v>
+        <v>-0.965</v>
       </c>
       <c r="R22" t="n">
-        <v>0.579</v>
+        <v>0.772</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1217</v>
+        <v>0.7129</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3569</v>
+        <v>0.5486</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7648</v>
+        <v>0.1642</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0029</v>
+        <v>-0.6317</v>
       </c>
       <c r="E23" t="n">
-        <v>0.545</v>
+        <v>0.0443</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5421</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="G23" t="n">
         <v>1.129</v>
@@ -2248,13 +2248,13 @@
         <v>0.965</v>
       </c>
       <c r="S23" t="n">
-        <v>0.9510999999999999</v>
+        <v>0.3166</v>
       </c>
       <c r="T23" t="n">
-        <v>1.1567</v>
+        <v>0.656</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2056</v>
+        <v>-0.3394</v>
       </c>
       <c r="V23" t="n">
         <v>-1.8842</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.9153</v>
+        <v>-1.3743</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.7635</v>
+        <v>-0.4631</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.1518</v>
+        <v>-0.9112</v>
       </c>
       <c r="G24" t="n">
         <v>-0.6411</v>
@@ -2326,13 +2326,13 @@
         <v>0.772</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6253</v>
+        <v>-0.0843</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4164</v>
+        <v>-0.116</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2089</v>
+        <v>0.0317</v>
       </c>
       <c r="V24" t="n">
         <v>-1.228</v>
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>34.5707</v>
+        <v>35.9059</v>
       </c>
       <c r="E25" t="n">
-        <v>19.9038</v>
+        <v>19.904</v>
       </c>
       <c r="F25" t="n">
-        <v>14.6668</v>
+        <v>16.0022</v>
       </c>
       <c r="G25" t="n">
-        <v>33.37199999999999</v>
+        <v>33.372</v>
       </c>
       <c r="H25" t="n">
         <v>11.7837</v>
@@ -2386,13 +2386,13 @@
         <v>15.0411</v>
       </c>
       <c r="M25" t="n">
-        <v>3.5733</v>
+        <v>3.573299999999999</v>
       </c>
       <c r="N25" t="n">
         <v>-2.9741</v>
       </c>
       <c r="O25" t="n">
-        <v>6.5475</v>
+        <v>6.547500000000001</v>
       </c>
       <c r="P25" t="n">
         <v>-3.8602</v>
@@ -2404,16 +2404,16 @@
         <v>15.4406</v>
       </c>
       <c r="S25" t="n">
-        <v>4.2434</v>
+        <v>5.578400000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>3.1067</v>
+        <v>3.1068</v>
       </c>
       <c r="U25" t="n">
-        <v>1.1366</v>
+        <v>2.4717</v>
       </c>
       <c r="V25" t="n">
-        <v>0.815400000000001</v>
+        <v>0.8154000000000001</v>
       </c>
       <c r="W25" t="n">
         <v>6.298999999999999</v>
